--- a/Data Analysis/VLOOKUP.xlsx
+++ b/Data Analysis/VLOOKUP.xlsx
@@ -167,7 +167,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -460,22 +460,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -888,14 +888,14 @@
         <v>36</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K5" s="22">
         <v>1</v>
       </c>
       <c r="L5" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>Coffee Mug</v>
+        <v>Wireless Mouse</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
@@ -1061,9 +1061,9 @@
       <c r="K11" s="22">
         <v>7</v>
       </c>
-      <c r="L11" s="19" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
+      <c r="L11" s="19" t="str">
+        <f>_xlfn.IFNA(VLOOKUP($J$11,$B$2:$E$12,2,FALSE),"Not Present")</f>
+        <v>Not Present</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1089,9 +1089,9 @@
       <c r="K12" s="24">
         <v>3</v>
       </c>
-      <c r="L12" s="21" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
+      <c r="L12" s="21" t="str">
+        <f>_xlfn.IFNA(VLOOKUP(J12,$B$2:$E$12,2,FALSE),"Not Present")</f>
+        <v>Not Present</v>
       </c>
     </row>
   </sheetData>
